--- a/Risultati/Excel/K=7.xlsx
+++ b/Risultati/Excel/K=7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\Risultati\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7940F04-383B-4A3B-B9AF-648A04458C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404BFD33-76C9-435F-A0E6-2BDB9CAA2F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D413EE3-C5FB-4387-91B4-93693FBB7B3F}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Confusion Matrix [[TN, FP], [FN, TP]]</t>
   </si>
   <si>
-    <t>RAW</t>
-  </si>
-  <si>
     <t>0.70</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>all-MiniLM-L6-v2</t>
   </si>
   <si>
-    <t>SEMANTIC</t>
-  </si>
-  <si>
     <t>0.7946</t>
   </si>
   <si>
@@ -201,6 +195,12 @@
   </si>
   <si>
     <t>[[12550, 944], [5326, 8215]]</t>
+  </si>
+  <si>
+    <t>ORIGINAL</t>
+  </si>
+  <si>
+    <t>EMBEDDING</t>
   </si>
 </sst>
 </file>
@@ -646,92 +646,92 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2">
         <v>2381</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
@@ -742,49 +742,49 @@
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>2381</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="N6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -795,49 +795,49 @@
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2">
         <v>2381</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
